--- a/fhir/ig/tei/0.2.2/StructureDefinition-ServiceRequestLE.xlsx
+++ b/fhir/ig/tei/0.2.2/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$103</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3892" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3855" uniqueCount="659">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T12:08:03-03:00</t>
+    <t>2026-04-30T10:23:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -634,22 +634,6 @@
   </si>
   <si>
     <t>Indica si corresponde a GES</t>
-  </si>
-  <si>
-    <t>ServiceRequest.extension:ProblemaSaludGES</t>
-  </si>
-  <si>
-    <t>ProblemaSaludGES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interoperabilidad.minsal.cl/fhir/ig/tei/StructureDefinition/ProblemaSaludGESTEI}
-</t>
-  </si>
-  <si>
-    <t>Indica a cual es el problema de salud GES que corresponde la interconsulta</t>
-  </si>
-  <si>
-    <t>Indica si corresponde a que problema de salud GES</t>
   </si>
   <si>
     <t>ServiceRequest.modifierExtension</t>
@@ -2411,20 +2395,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO104"/>
+  <dimension ref="A1:AO103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.5859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.91796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="31.46484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.80859375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="29.9140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="36.47265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="101.90234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="97.7578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2433,27 +2417,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="34.80859375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="109.59375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.13671875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="30.87890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="105.46484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.34765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.27734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="73.67578125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="141.90625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="29.45703125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="53.2421875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9296875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="72.94921875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="135.91796875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="52.66015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4796,46 +4780,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C21" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I21" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I21" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4883,7 +4869,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4892,7 +4878,7 @@
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>142</v>
@@ -4904,7 +4890,7 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>82</v>
@@ -4913,16 +4899,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4932,29 +4918,27 @@
         <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="J22" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>136</v>
+        <v>205</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -5002,7 +4986,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5014,30 +4998,30 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5048,29 +5032,27 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5119,53 +5101,53 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -5177,7 +5159,7 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>221</v>
@@ -5185,7 +5167,9 @@
       <c r="M24" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5222,31 +5206,31 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5255,7 +5239,7 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5273,26 +5257,26 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>226</v>
@@ -5301,9 +5285,11 @@
         <v>227</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5327,52 +5313,52 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
@@ -5383,10 +5369,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5403,25 +5389,25 @@
         <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5446,13 +5432,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5470,7 +5456,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5488,10 +5474,10 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>134</v>
+        <v>245</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
@@ -5502,10 +5488,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5528,19 +5514,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>105</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5553,7 +5539,7 @@
         <v>82</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>82</v>
@@ -5565,13 +5551,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5589,7 +5575,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5607,10 +5593,10 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
@@ -5619,12 +5605,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5638,7 +5624,7 @@
         <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5647,20 +5633,18 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5672,7 +5656,7 @@
         <v>82</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>82</v>
@@ -5708,7 +5692,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5726,10 +5710,10 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
@@ -5738,12 +5722,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5757,7 +5741,7 @@
         <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
@@ -5766,17 +5750,15 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5789,7 +5771,7 @@
         <v>82</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>82</v>
@@ -5825,7 +5807,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5843,10 +5825,10 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
@@ -5857,10 +5839,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5883,15 +5865,17 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5940,7 +5924,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5958,10 +5942,10 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>82</v>
@@ -5972,10 +5956,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5986,7 +5970,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5998,16 +5982,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6057,13 +6041,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -6072,13 +6056,13 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6089,10 +6073,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6115,16 +6099,16 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>284</v>
+        <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6174,7 +6158,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6189,13 +6173,13 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -6213,7 +6197,7 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6232,17 +6216,15 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>105</v>
+        <v>293</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6306,13 +6288,13 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6323,14 +6305,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6349,13 +6331,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6406,7 +6388,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6421,13 +6403,13 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
@@ -6438,21 +6420,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6464,16 +6446,20 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>306</v>
+        <v>205</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6521,13 +6507,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -6536,13 +6522,13 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -6551,48 +6537,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>210</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6601,7 +6585,7 @@
         <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>82</v>
@@ -6616,13 +6600,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6640,10 +6624,10 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>91</v>
@@ -6655,27 +6639,27 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6701,13 +6685,13 @@
         <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6718,7 +6702,7 @@
         <v>82</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>11</v>
+        <v>331</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>82</v>
@@ -6733,13 +6717,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6757,7 +6741,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>91</v>
@@ -6772,27 +6756,27 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>328</v>
+        <v>134</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6800,7 +6784,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>91</v>
@@ -6809,24 +6793,26 @@
         <v>92</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6835,7 +6821,7 @@
         <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>82</v>
@@ -6850,37 +6836,35 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Y38" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y38" s="2"/>
+      <c r="Z38" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="AG38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6889,27 +6873,27 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>134</v>
+        <v>343</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6923,29 +6907,25 @@
         <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>216</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6969,11 +6949,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6991,31 +6973,31 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>218</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>219</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7023,21 +7005,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7049,7 +7031,7 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>221</v>
@@ -7057,7 +7039,9 @@
       <c r="M40" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N40" s="2"/>
+      <c r="N40" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7094,31 +7078,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7127,7 +7111,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7136,46 +7120,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>136</v>
+        <v>348</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>226</v>
+        <v>349</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7211,19 +7197,19 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>229</v>
+        <v>353</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7235,16 +7221,16 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>224</v>
+        <v>355</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -7253,12 +7239,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7266,35 +7252,31 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>353</v>
+        <v>215</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>354</v>
+        <v>216</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7342,28 +7324,28 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>358</v>
+        <v>218</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>360</v>
+        <v>219</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -7374,21 +7356,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7400,7 +7382,7 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>221</v>
@@ -7408,7 +7390,9 @@
       <c r="M43" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N43" s="2"/>
+      <c r="N43" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7445,31 +7429,31 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7478,7 +7462,7 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -7487,46 +7471,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>226</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>227</v>
+        <v>360</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7562,40 +7548,40 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>229</v>
+        <v>363</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>224</v>
+        <v>365</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7604,12 +7590,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7623,7 +7609,7 @@
         <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7632,20 +7618,18 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7693,7 +7677,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7711,10 +7695,10 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7723,12 +7707,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7736,13 +7720,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>82</v>
@@ -7751,18 +7735,18 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7810,7 +7794,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7828,10 +7812,10 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7842,10 +7826,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7853,7 +7837,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>91</v>
@@ -7868,17 +7852,17 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>111</v>
+        <v>215</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7927,7 +7911,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7945,10 +7929,10 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
@@ -7957,12 +7941,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7976,7 +7960,7 @@
         <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -7985,17 +7969,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>220</v>
+        <v>388</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8044,7 +8030,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8062,10 +8048,10 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>82</v>
@@ -8076,10 +8062,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8102,19 +8088,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>393</v>
+        <v>215</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8163,7 +8149,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8181,10 +8167,10 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8193,12 +8179,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8212,7 +8198,7 @@
         <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -8221,68 +8207,66 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N50" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q50" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="R50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8297,27 +8281,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8331,30 +8315,34 @@
         <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I51" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>111</v>
+        <v>388</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>82</v>
@@ -8375,31 +8363,31 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8414,31 +8402,31 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8448,79 +8436,73 @@
         <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>393</v>
+        <v>236</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="N52" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y52" s="2"/>
+      <c r="Z52" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q52" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="R52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8535,31 +8517,31 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8569,26 +8551,24 @@
         <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>429</v>
+        <v>216</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8613,11 +8593,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8635,7 +8617,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>427</v>
+        <v>218</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8647,41 +8629,41 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>435</v>
+        <v>219</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8693,7 +8675,7 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>221</v>
@@ -8701,7 +8683,9 @@
       <c r="M54" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N54" s="2"/>
+      <c r="N54" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8738,31 +8722,31 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8771,7 +8755,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8780,46 +8764,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>348</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>226</v>
+        <v>349</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8855,19 +8841,19 @@
         <v>82</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>229</v>
+        <v>353</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8879,16 +8865,16 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>224</v>
+        <v>355</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>82</v>
@@ -8897,12 +8883,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8910,35 +8896,31 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>353</v>
+        <v>215</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>354</v>
+        <v>216</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -8986,28 +8968,28 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>358</v>
+        <v>218</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>360</v>
+        <v>219</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>82</v>
@@ -9018,21 +9000,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9044,7 +9026,7 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>221</v>
@@ -9052,7 +9034,9 @@
       <c r="M57" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N57" s="2"/>
+      <c r="N57" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9089,31 +9073,31 @@
         <v>82</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9122,7 +9106,7 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9131,46 +9115,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>226</v>
+        <v>359</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>227</v>
+        <v>360</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9206,40 +9192,40 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>229</v>
+        <v>363</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>224</v>
+        <v>365</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9248,12 +9234,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9267,7 +9253,7 @@
         <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9276,20 +9262,18 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9337,7 +9321,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9355,10 +9339,10 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9367,12 +9351,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9380,13 +9364,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
@@ -9395,18 +9379,18 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9454,7 +9438,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9472,10 +9456,10 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9486,10 +9470,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9497,7 +9481,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>91</v>
@@ -9512,17 +9496,17 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>111</v>
+        <v>215</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9571,7 +9555,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9589,10 +9573,10 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9601,12 +9585,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9620,7 +9604,7 @@
         <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
@@ -9629,17 +9613,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>220</v>
+        <v>388</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O62" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9688,7 +9674,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9706,10 +9692,10 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9720,10 +9706,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9746,19 +9732,19 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>393</v>
+        <v>215</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9807,7 +9793,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9825,10 +9811,10 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9839,21 +9825,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9865,20 +9851,18 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>402</v>
+        <v>446</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>403</v>
+        <v>447</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9902,13 +9886,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9926,16 +9910,16 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>406</v>
+        <v>444</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>103</v>
@@ -9944,35 +9928,35 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>407</v>
+        <v>453</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9984,18 +9968,18 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>241</v>
+        <v>455</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10019,40 +10003,40 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="Y65" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>103</v>
@@ -10061,24 +10045,24 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10086,13 +10070,13 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>82</v>
@@ -10101,18 +10085,16 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>463</v>
-      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10160,10 +10142,10 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>91</v>
@@ -10175,41 +10157,41 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
@@ -10218,13 +10200,13 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10275,10 +10257,10 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>91</v>
@@ -10290,31 +10272,31 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10333,13 +10315,13 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10390,7 +10372,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10405,31 +10387,31 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10448,13 +10430,13 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10481,13 +10463,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10505,7 +10487,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10520,31 +10502,31 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10554,7 +10536,7 @@
         <v>91</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
@@ -10563,13 +10545,13 @@
         <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10596,13 +10578,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10620,7 +10602,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10635,31 +10617,31 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10678,15 +10660,17 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10735,7 +10719,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10750,31 +10734,31 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10784,7 +10768,7 @@
         <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
@@ -10793,16 +10777,16 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>514</v>
+        <v>236</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10828,13 +10812,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10852,7 +10836,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10867,31 +10851,31 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10901,7 +10885,7 @@
         <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
@@ -10910,16 +10894,16 @@
         <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>241</v>
+        <v>509</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10945,37 +10929,37 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="Z73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AA73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
@@ -10984,16 +10968,16 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11001,14 +10985,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11027,17 +11011,15 @@
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>514</v>
+        <v>236</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11062,13 +11044,11 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11086,7 +11066,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11101,22 +11081,22 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>541</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>542</v>
       </c>
@@ -11135,22 +11115,22 @@
         <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>543</v>
+        <v>216</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>544</v>
+        <v>217</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11177,11 +11157,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11199,19 +11181,19 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>542</v>
+        <v>218</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11220,10 +11202,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>546</v>
+        <v>219</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11231,21 +11213,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11257,7 +11239,7 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>221</v>
@@ -11265,7 +11247,9 @@
       <c r="M76" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N76" s="2"/>
+      <c r="N76" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11302,31 +11286,31 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11335,7 +11319,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11344,46 +11328,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>136</v>
+        <v>348</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>226</v>
+        <v>349</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11419,19 +11405,19 @@
         <v>82</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>229</v>
+        <v>353</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11443,16 +11429,16 @@
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>224</v>
+        <v>355</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11461,12 +11447,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11474,35 +11460,31 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>353</v>
+        <v>215</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>354</v>
+        <v>216</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11550,28 +11532,28 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>358</v>
+        <v>218</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>360</v>
+        <v>219</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11582,21 +11564,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11608,7 +11590,7 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>221</v>
@@ -11616,7 +11598,9 @@
       <c r="M79" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N79" s="2"/>
+      <c r="N79" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11653,31 +11637,31 @@
         <v>82</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11686,7 +11670,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11695,46 +11679,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>226</v>
+        <v>359</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>227</v>
+        <v>360</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11770,40 +11756,40 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>229</v>
+        <v>363</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>224</v>
+        <v>365</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11812,12 +11798,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11825,13 +11811,13 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>82</v>
@@ -11840,20 +11826,18 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -11901,7 +11885,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11919,10 +11903,10 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -11931,12 +11915,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11944,13 +11928,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
@@ -11959,18 +11943,18 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12018,7 +12002,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12036,10 +12020,10 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12050,10 +12034,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12061,7 +12045,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>91</v>
@@ -12076,17 +12060,17 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>215</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12135,7 +12119,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12153,10 +12137,10 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12165,12 +12149,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12184,7 +12168,7 @@
         <v>91</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12193,17 +12177,19 @@
         <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>220</v>
+        <v>388</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O84" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12252,7 +12238,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12270,10 +12256,10 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12284,10 +12270,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12310,19 +12296,19 @@
         <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>393</v>
+        <v>215</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12371,7 +12357,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12389,10 +12375,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12403,10 +12389,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12417,7 +12403,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12429,20 +12415,16 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>220</v>
+        <v>554</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>402</v>
+        <v>555</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12490,13 +12472,13 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>406</v>
+        <v>553</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
@@ -12508,19 +12490,19 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>408</v>
+        <v>557</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>558</v>
       </c>
@@ -12536,10 +12518,10 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>82</v>
@@ -12548,15 +12530,17 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12581,13 +12565,11 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12620,27 +12602,27 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>82</v>
+        <v>563</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>82</v>
+        <v>564</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>533</v>
+        <v>566</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12651,10 +12633,10 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>82</v>
@@ -12663,16 +12645,16 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>241</v>
+        <v>568</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12698,29 +12680,31 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Y88" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12735,16 +12719,16 @@
         <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12752,10 +12736,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12775,20 +12759,18 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12837,7 +12819,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12852,16 +12834,16 @@
         <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -12869,14 +12851,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>583</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12886,7 +12868,7 @@
         <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>82</v>
@@ -12895,15 +12877,17 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -12940,19 +12924,19 @@
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12967,13 +12951,13 @@
         <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
@@ -12982,23 +12966,25 @@
         <v>82</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="D91" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>92</v>
@@ -13010,16 +12996,16 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13057,19 +13043,19 @@
         <v>82</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13084,13 +13070,13 @@
         <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
@@ -13101,23 +13087,23 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C92" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="B92" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>599</v>
-      </c>
       <c r="D92" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>92</v>
@@ -13129,16 +13115,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="L92" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="M92" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13188,7 +13174,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13203,13 +13189,13 @@
         <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
@@ -13220,23 +13206,23 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C93" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="B93" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>603</v>
-      </c>
       <c r="D93" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>92</v>
@@ -13248,16 +13234,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L93" t="s" s="2">
-        <v>605</v>
-      </c>
       <c r="M93" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13307,7 +13293,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13322,13 +13308,13 @@
         <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
@@ -13339,16 +13325,16 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C94" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="B94" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>607</v>
-      </c>
       <c r="D94" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13367,16 +13353,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="L94" t="s" s="2">
-        <v>609</v>
-      </c>
       <c r="M94" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13426,7 +13412,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13441,13 +13427,13 @@
         <v>103</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13458,16 +13444,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C95" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="B95" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>611</v>
-      </c>
       <c r="D95" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13486,16 +13472,16 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="L95" t="s" s="2">
-        <v>613</v>
-      </c>
       <c r="M95" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13545,7 +13531,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13560,13 +13546,13 @@
         <v>103</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13577,16 +13563,16 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="B96" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>615</v>
-      </c>
       <c r="D96" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13605,16 +13591,16 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="L96" t="s" s="2">
-        <v>617</v>
-      </c>
       <c r="M96" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13664,7 +13650,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13679,13 +13665,13 @@
         <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13696,23 +13682,23 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="B97" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>619</v>
-      </c>
       <c r="D97" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>92</v>
@@ -13724,16 +13710,16 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="L97" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="M97" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13783,7 +13769,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13798,13 +13784,13 @@
         <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
@@ -13815,16 +13801,16 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C98" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="B98" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>623</v>
-      </c>
       <c r="D98" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13843,16 +13829,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="L98" t="s" s="2">
-        <v>625</v>
-      </c>
       <c r="M98" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13902,7 +13888,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13917,13 +13903,13 @@
         <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
@@ -13932,18 +13918,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>627</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>588</v>
+        <v>82</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13953,25 +13937,25 @@
         <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J99" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K99" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14021,7 +14005,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>587</v>
+        <v>625</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14036,13 +14020,13 @@
         <v>103</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>595</v>
+        <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>596</v>
+        <v>630</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>597</v>
+        <v>631</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
@@ -14053,14 +14037,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14079,18 +14063,20 @@
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>631</v>
+        <v>236</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>637</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14114,13 +14100,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>82</v>
+        <v>638</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14138,7 +14124,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14156,28 +14142,28 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>82</v>
+        <v>641</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>638</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14193,23 +14179,19 @@
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>241</v>
+        <v>643</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>639</v>
+        <v>51</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>642</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14233,13 +14215,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>643</v>
+        <v>82</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14257,7 +14239,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14272,27 +14254,27 @@
         <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>82</v>
+        <v>645</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>635</v>
+        <v>453</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14303,7 +14285,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>82</v>
@@ -14312,16 +14294,16 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>648</v>
+        <v>215</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>51</v>
+        <v>649</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14372,13 +14354,13 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
@@ -14387,10 +14369,10 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>651</v>
@@ -14399,15 +14381,15 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>652</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14418,7 +14400,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -14427,10 +14409,10 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>220</v>
+        <v>653</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>654</v>
@@ -14438,7 +14420,9 @@
       <c r="M103" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="N103" s="2"/>
+      <c r="N103" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14487,13 +14471,13 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
@@ -14502,140 +14486,23 @@
         <v>103</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>458</v>
+        <v>134</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO104">
+  <autoFilter ref="A1:AO103">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14645,7 +14512,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI103">
+  <conditionalFormatting sqref="A2:AI102">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
